--- a/Simulations/input/Zr_input_parameters.xlsx
+++ b/Simulations/input/Zr_input_parameters.xlsx
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="9" min="1" max="1"/>
@@ -6992,11 +6992,6 @@
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
